--- a/InputData/fuels/BPTbCP/BAU Pollutants Taxed by Carbon Pricing.xlsx
+++ b/InputData/fuels/BPTbCP/BAU Pollutants Taxed by Carbon Pricing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\fuels\BPTbCP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-dc-replay\InputData\fuels\BPTbCP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5A4D95-5618-4828-8B24-3AA1B8BA3133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F109B0F5-BD48-4D23-AF2A-67FB4BD4DE4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="64560" yWindow="1530" windowWidth="20820" windowHeight="14820" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -21,17 +21,28 @@
     <sheet name="BPTbCP-districtheat" sheetId="10" r:id="rId6"/>
     <sheet name="BPTbCP-hydrogen" sheetId="13" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="86">
   <si>
     <t>Sources:</t>
   </si>
@@ -280,6 +291,15 @@
   </si>
   <si>
     <t>building type</t>
+  </si>
+  <si>
+    <t>data centers</t>
+  </si>
+  <si>
+    <t>Data centers</t>
+  </si>
+  <si>
+    <t>Data centers are a separate building type in the buildings sector. Carbon pricing covers the same pollutants for data centers as for commercial buildings, so the data-centers row copies the commercial row.</t>
   </si>
 </sst>
 </file>
@@ -331,10 +351,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -615,45 +638,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -667,12 +698,12 @@
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>45</v>
       </c>
@@ -713,7 +744,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>46</v>
       </c>
@@ -754,7 +785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>47</v>
       </c>
@@ -795,7 +826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>48</v>
       </c>
@@ -836,7 +867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -877,7 +908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>50</v>
       </c>
@@ -918,7 +949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -970,12 +1001,12 @@
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:M25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>44</v>
       </c>
@@ -1016,7 +1047,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1057,7 +1088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1098,7 +1129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1139,7 +1170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1180,7 +1211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1221,7 +1252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1262,7 +1293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1303,7 +1334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1344,7 +1375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1385,7 +1416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1426,7 +1457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1467,7 +1498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>31</v>
       </c>
@@ -1508,7 +1539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1549,7 +1580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -1590,7 +1621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -1631,7 +1662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1672,7 +1703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>36</v>
       </c>
@@ -1713,7 +1744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1754,7 +1785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -1795,7 +1826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -1836,7 +1867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1877,7 +1908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>41</v>
       </c>
@@ -1918,7 +1949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>42</v>
       </c>
@@ -1959,7 +1990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -2010,13 +2041,13 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>82</v>
       </c>
@@ -2057,7 +2088,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>52</v>
       </c>
@@ -2098,7 +2129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -2139,7 +2170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -2177,6 +2208,59 @@
         <v>1</v>
       </c>
       <c r="M4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5">
+        <f>B4</f>
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <f>C4</f>
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f>D4</f>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f>E4</f>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f>F4</f>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f>G4</f>
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <f>H4</f>
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <f>I4</f>
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <f>J4</f>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f>K4</f>
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <f>L4</f>
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <f>M4</f>
         <v>1</v>
       </c>
     </row>
@@ -2191,12 +2275,12 @@
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>81</v>
       </c>
@@ -2237,7 +2321,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -2278,7 +2362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -2319,7 +2403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -2360,7 +2444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -2401,7 +2485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>59</v>
       </c>
@@ -2442,7 +2526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -2483,7 +2567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>61</v>
       </c>
@@ -2524,7 +2608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>62</v>
       </c>
@@ -2565,7 +2649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>63</v>
       </c>
@@ -2606,7 +2690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>64</v>
       </c>
@@ -2647,7 +2731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -2688,7 +2772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>66</v>
       </c>
@@ -2729,7 +2813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -2770,7 +2854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>68</v>
       </c>
@@ -2811,7 +2895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>69</v>
       </c>
@@ -2852,7 +2936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -2893,7 +2977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>71</v>
       </c>
@@ -2934,7 +3018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>72</v>
       </c>
@@ -2975,7 +3059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>73</v>
       </c>
@@ -3016,7 +3100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>74</v>
       </c>
@@ -3057,7 +3141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>75</v>
       </c>
@@ -3098,7 +3182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>76</v>
       </c>
@@ -3139,7 +3223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>77</v>
       </c>
@@ -3180,7 +3264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>78</v>
       </c>
@@ -3221,7 +3305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>79</v>
       </c>
@@ -3273,12 +3357,12 @@
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -3286,7 +3370,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3294,7 +3378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3302,7 +3386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3310,7 +3394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -3318,7 +3402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3326,7 +3410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -3334,7 +3418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3342,7 +3426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -3350,7 +3434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -3358,7 +3442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -3366,7 +3450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -3374,7 +3458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -3393,12 +3477,12 @@
     <tabColor theme="8" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -3406,7 +3490,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3414,7 +3498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3422,7 +3506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -3430,7 +3514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -3438,7 +3522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3446,7 +3530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -3454,7 +3538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -3462,7 +3546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -3470,7 +3554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -3478,7 +3562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -3486,7 +3570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -3494,7 +3578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
